--- a/data/nzd0084/nzd0084.xlsx
+++ b/data/nzd0084/nzd0084.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F338"/>
+  <dimension ref="A1:F339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8548,6 +8548,30 @@
       <c r="F338" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="C339" t="n">
+        <v>325.8</v>
+      </c>
+      <c r="D339" t="n">
+        <v>329.56</v>
+      </c>
+      <c r="E339" t="n">
+        <v>333.85</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B347"/>
+  <dimension ref="A1:B348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12035,6 +12059,16 @@
       </c>
       <c r="B347" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -12203,28 +12237,28 @@
         <v>0.0935</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2305748435527153</v>
+        <v>0.2260272038639049</v>
       </c>
       <c r="J2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K2" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0629778151580983</v>
+        <v>0.06087795616987002</v>
       </c>
       <c r="M2" t="n">
-        <v>4.960487868005631</v>
+        <v>4.963348969917563</v>
       </c>
       <c r="N2" t="n">
-        <v>39.83456437907711</v>
+        <v>39.85975627863699</v>
       </c>
       <c r="O2" t="n">
-        <v>6.311462934936488</v>
+        <v>6.31345834536326</v>
       </c>
       <c r="P2" t="n">
-        <v>330.7515152941917</v>
+        <v>330.7993816808057</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12285,28 +12319,28 @@
         <v>0.0747</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3253141547792809</v>
+        <v>0.3206312567267938</v>
       </c>
       <c r="J3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1099513423792995</v>
+        <v>0.1075061103690004</v>
       </c>
       <c r="M3" t="n">
-        <v>5.247786079201139</v>
+        <v>5.249738078218361</v>
       </c>
       <c r="N3" t="n">
-        <v>43.14128509178664</v>
+        <v>43.16532941671586</v>
       </c>
       <c r="O3" t="n">
-        <v>6.568202576944977</v>
+        <v>6.570032680034084</v>
       </c>
       <c r="P3" t="n">
-        <v>324.4751209133682</v>
+        <v>324.5244109679884</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12367,28 +12401,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3145861061413803</v>
+        <v>0.3108970858593334</v>
       </c>
       <c r="J4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1010984339930244</v>
+        <v>0.09943543372957953</v>
       </c>
       <c r="M4" t="n">
-        <v>5.304398217495359</v>
+        <v>5.303864986006327</v>
       </c>
       <c r="N4" t="n">
-        <v>44.31193629925829</v>
+        <v>44.27496514981708</v>
       </c>
       <c r="O4" t="n">
-        <v>6.656721137261068</v>
+        <v>6.653943578797244</v>
       </c>
       <c r="P4" t="n">
-        <v>326.9874466092296</v>
+        <v>327.0262755585593</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12445,28 +12479,28 @@
         <v>0.0931</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1778598375914784</v>
+        <v>0.1743657078436075</v>
       </c>
       <c r="J5" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K5" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0385888805830551</v>
+        <v>0.03732811083649279</v>
       </c>
       <c r="M5" t="n">
-        <v>5.042960527156967</v>
+        <v>5.041713311869456</v>
       </c>
       <c r="N5" t="n">
-        <v>39.68959677148202</v>
+        <v>39.65661822108981</v>
       </c>
       <c r="O5" t="n">
-        <v>6.299967997655386</v>
+        <v>6.297350095166205</v>
       </c>
       <c r="P5" t="n">
-        <v>334.5645746359219</v>
+        <v>334.6013522561459</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12504,7 +12538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F338"/>
+  <dimension ref="A1:F339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23323,6 +23357,38 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>-35.50792848251519,174.47268646969403</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>-35.50855315293113,174.47315649642886</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-35.509137881949975,174.47369676420453</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-35.50971987855471,174.47424182973214</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0084/nzd0084.xlsx
+++ b/data/nzd0084/nzd0084.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F339"/>
+  <dimension ref="A1:F340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8570,6 +8570,30 @@
         <v>333.85</v>
       </c>
       <c r="F339" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>326.05</v>
+      </c>
+      <c r="C340" t="n">
+        <v>321.09</v>
+      </c>
+      <c r="D340" t="n">
+        <v>325.07</v>
+      </c>
+      <c r="E340" t="n">
+        <v>335.6</v>
+      </c>
+      <c r="F340" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8586,7 +8610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B348"/>
+  <dimension ref="A1:B349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12069,6 +12093,16 @@
       </c>
       <c r="B348" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -12237,28 +12271,28 @@
         <v>0.0935</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2260272038639049</v>
+        <v>0.2190862906552151</v>
       </c>
       <c r="J2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06087795616987002</v>
+        <v>0.05735038148679727</v>
       </c>
       <c r="M2" t="n">
-        <v>4.963348969917563</v>
+        <v>4.976007968713522</v>
       </c>
       <c r="N2" t="n">
-        <v>39.85975627863699</v>
+        <v>40.07602025724855</v>
       </c>
       <c r="O2" t="n">
-        <v>6.31345834536326</v>
+        <v>6.330562396600206</v>
       </c>
       <c r="P2" t="n">
-        <v>330.7993816808057</v>
+        <v>330.8726852107042</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12319,28 +12353,28 @@
         <v>0.0747</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3206312567267938</v>
+        <v>0.3129308127719089</v>
       </c>
       <c r="J3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1075061103690004</v>
+        <v>0.102726580340227</v>
       </c>
       <c r="M3" t="n">
-        <v>5.249738078218361</v>
+        <v>5.263709727567505</v>
       </c>
       <c r="N3" t="n">
-        <v>43.16532941671586</v>
+        <v>43.44890395602953</v>
       </c>
       <c r="O3" t="n">
-        <v>6.570032680034084</v>
+        <v>6.591578259872937</v>
       </c>
       <c r="P3" t="n">
-        <v>324.5244109679884</v>
+        <v>324.6057359617905</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12401,28 +12435,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3108970858593334</v>
+        <v>0.3043249662738182</v>
       </c>
       <c r="J4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09943543372957953</v>
+        <v>0.09572113116414771</v>
       </c>
       <c r="M4" t="n">
-        <v>5.303864986006327</v>
+        <v>5.315474108702057</v>
       </c>
       <c r="N4" t="n">
-        <v>44.27496514981708</v>
+        <v>44.4436708982202</v>
       </c>
       <c r="O4" t="n">
-        <v>6.653943578797244</v>
+        <v>6.666608650447407</v>
       </c>
       <c r="P4" t="n">
-        <v>327.0262755585593</v>
+        <v>327.0956842300192</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12479,28 +12513,28 @@
         <v>0.0931</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1743657078436075</v>
+        <v>0.1720382004889084</v>
       </c>
       <c r="J5" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K5" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03732811083649279</v>
+        <v>0.03659762316815351</v>
       </c>
       <c r="M5" t="n">
-        <v>5.041713311869456</v>
+        <v>5.035872752878408</v>
       </c>
       <c r="N5" t="n">
-        <v>39.65661822108981</v>
+        <v>39.57717693388281</v>
       </c>
       <c r="O5" t="n">
-        <v>6.297350095166205</v>
+        <v>6.291039416017262</v>
       </c>
       <c r="P5" t="n">
-        <v>334.6013522561459</v>
+        <v>334.6259332442428</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12538,7 +12572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F339"/>
+  <dimension ref="A1:F340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23389,6 +23423,38 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-35.50794778180691,174.4726525260541</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-35.50857739294407,174.47311386298355</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-35.50916098985534,174.4736561219515</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-35.50971087208106,174.47425767031638</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0084/nzd0084.xlsx
+++ b/data/nzd0084/nzd0084.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F340"/>
+  <dimension ref="A1:F341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8596,6 +8596,30 @@
       <c r="F340" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>323.55</v>
+      </c>
+      <c r="C341" t="n">
+        <v>319.67</v>
+      </c>
+      <c r="D341" t="n">
+        <v>325.51</v>
+      </c>
+      <c r="E341" t="n">
+        <v>339.44</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B349"/>
+  <dimension ref="A1:B350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12103,6 +12127,16 @@
       </c>
       <c r="B349" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -12271,28 +12305,28 @@
         <v>0.0935</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2190862906552151</v>
+        <v>0.2105054917701177</v>
       </c>
       <c r="J2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05735038148679727</v>
+        <v>0.0529285327317025</v>
       </c>
       <c r="M2" t="n">
-        <v>4.976007968713522</v>
+        <v>4.995243799360757</v>
       </c>
       <c r="N2" t="n">
-        <v>40.07602025724855</v>
+        <v>40.45965811764172</v>
       </c>
       <c r="O2" t="n">
-        <v>6.330562396600206</v>
+        <v>6.360790683369618</v>
       </c>
       <c r="P2" t="n">
-        <v>330.8726852107042</v>
+        <v>330.963983479554</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12353,28 +12387,28 @@
         <v>0.0747</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3129308127719089</v>
+        <v>0.3042858844347928</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L3" t="n">
-        <v>0.102726580340227</v>
+        <v>0.09730480337684266</v>
       </c>
       <c r="M3" t="n">
-        <v>5.263709727567505</v>
+        <v>5.28128156785322</v>
       </c>
       <c r="N3" t="n">
-        <v>43.44890395602953</v>
+        <v>43.8301457290606</v>
       </c>
       <c r="O3" t="n">
-        <v>6.591578259872937</v>
+        <v>6.620433953228489</v>
       </c>
       <c r="P3" t="n">
-        <v>324.6057359617905</v>
+        <v>324.6977165573129</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12435,28 +12469,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3043249662738182</v>
+        <v>0.2980176844663289</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09572113116414771</v>
+        <v>0.09227086453514044</v>
       </c>
       <c r="M4" t="n">
-        <v>5.315474108702057</v>
+        <v>5.325804853217275</v>
       </c>
       <c r="N4" t="n">
-        <v>44.4436708982202</v>
+        <v>44.58391555830516</v>
       </c>
       <c r="O4" t="n">
-        <v>6.666608650447407</v>
+        <v>6.677118806663931</v>
       </c>
       <c r="P4" t="n">
-        <v>327.0956842300192</v>
+        <v>327.1627926563886</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12513,28 +12547,28 @@
         <v>0.0931</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1720382004889084</v>
+        <v>0.172209742244414</v>
       </c>
       <c r="J5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03659762316815351</v>
+        <v>0.03693234477234464</v>
       </c>
       <c r="M5" t="n">
-        <v>5.035872752878408</v>
+        <v>5.02193854053306</v>
       </c>
       <c r="N5" t="n">
-        <v>39.57717693388281</v>
+        <v>39.46097390223545</v>
       </c>
       <c r="O5" t="n">
-        <v>6.291039416017262</v>
+        <v>6.281797028099161</v>
       </c>
       <c r="P5" t="n">
-        <v>334.6259332442428</v>
+        <v>334.6241080685775</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12572,7 +12606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F340"/>
+  <dimension ref="A1:F341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23455,6 +23489,38 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-35.50796064799626,174.4726298969517</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-35.508584700970594,174.47310100958308</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-35.50915872538414,174.4736601047123</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-35.50969110929751,174.47429242907157</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0084/nzd0084.xlsx
+++ b/data/nzd0084/nzd0084.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F341"/>
+  <dimension ref="A1:F343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8620,6 +8620,54 @@
       <c r="F341" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>325.24</v>
+      </c>
+      <c r="C342" t="n">
+        <v>317.82</v>
+      </c>
+      <c r="D342" t="n">
+        <v>321.81</v>
+      </c>
+      <c r="E342" t="n">
+        <v>334.97</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>329.13</v>
+      </c>
+      <c r="C343" t="n">
+        <v>319.82</v>
+      </c>
+      <c r="D343" t="n">
+        <v>321.92</v>
+      </c>
+      <c r="E343" t="n">
+        <v>330.74</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B350"/>
+  <dimension ref="A1:B352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12137,6 +12185,26 @@
       </c>
       <c r="B350" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -12305,28 +12373,28 @@
         <v>0.0935</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2105054917701177</v>
+        <v>0.1983463701878613</v>
       </c>
       <c r="J2" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K2" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0529285327317025</v>
+        <v>0.04736185929999293</v>
       </c>
       <c r="M2" t="n">
-        <v>4.995243799360757</v>
+        <v>5.014011704970658</v>
       </c>
       <c r="N2" t="n">
-        <v>40.45965811764172</v>
+        <v>40.74907797522137</v>
       </c>
       <c r="O2" t="n">
-        <v>6.360790683369618</v>
+        <v>6.383500448439036</v>
       </c>
       <c r="P2" t="n">
-        <v>330.963983479554</v>
+        <v>331.0940218040446</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12387,28 +12455,28 @@
         <v>0.0747</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3042858844347928</v>
+        <v>0.2861597981759126</v>
       </c>
       <c r="J3" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K3" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09730480337684266</v>
+        <v>0.08620561976481356</v>
       </c>
       <c r="M3" t="n">
-        <v>5.28128156785322</v>
+        <v>5.319579249647496</v>
       </c>
       <c r="N3" t="n">
-        <v>43.8301457290606</v>
+        <v>44.69924587403706</v>
       </c>
       <c r="O3" t="n">
-        <v>6.620433953228489</v>
+        <v>6.685749462404126</v>
       </c>
       <c r="P3" t="n">
-        <v>324.6977165573129</v>
+        <v>324.8915805184054</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12469,28 +12537,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2980176844663289</v>
+        <v>0.2808612433703923</v>
       </c>
       <c r="J4" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K4" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09227086453514044</v>
+        <v>0.08224894414496497</v>
       </c>
       <c r="M4" t="n">
-        <v>5.325804853217275</v>
+        <v>5.365437986576376</v>
       </c>
       <c r="N4" t="n">
-        <v>44.58391555830516</v>
+        <v>45.32608822120738</v>
       </c>
       <c r="O4" t="n">
-        <v>6.677118806663931</v>
+        <v>6.732465240995112</v>
       </c>
       <c r="P4" t="n">
-        <v>327.1627926563886</v>
+        <v>327.3462909936816</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12547,28 +12615,28 @@
         <v>0.0931</v>
       </c>
       <c r="I5" t="n">
-        <v>0.172209742244414</v>
+        <v>0.1639667486641481</v>
       </c>
       <c r="J5" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K5" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03693234477234464</v>
+        <v>0.03387300834976104</v>
       </c>
       <c r="M5" t="n">
-        <v>5.02193854053306</v>
+        <v>5.024570234192004</v>
       </c>
       <c r="N5" t="n">
-        <v>39.46097390223545</v>
+        <v>39.48772073471324</v>
       </c>
       <c r="O5" t="n">
-        <v>6.281797028099161</v>
+        <v>6.283925583161631</v>
       </c>
       <c r="P5" t="n">
-        <v>334.6241080685775</v>
+        <v>334.7122837805551</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12606,7 +12674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F341"/>
+  <dimension ref="A1:F343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23521,6 +23589,70 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-35.507951950452714,174.47264519422572</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-35.50859422198907,174.47308426395213</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-35.50917776752446,174.4736266133076</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-35.5097141144118,174.47425196770646</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-35.507931930656,174.47268040509823</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-35.508583928996025,174.47310236733676</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-35.5091772014069,174.47362760899827</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-35.50973588434009,174.47421367874216</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0084/nzd0084.xlsx
+++ b/data/nzd0084/nzd0084.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F343"/>
+  <dimension ref="A1:F344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8668,6 +8668,30 @@
       <c r="F343" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>328.39</v>
+      </c>
+      <c r="C344" t="n">
+        <v>320.56</v>
+      </c>
+      <c r="D344" t="n">
+        <v>322.98</v>
+      </c>
+      <c r="E344" t="n">
+        <v>330.42</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B352"/>
+  <dimension ref="A1:B353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12205,6 +12229,16 @@
       </c>
       <c r="B352" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -12373,28 +12407,28 @@
         <v>0.0935</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1983463701878613</v>
+        <v>0.193182116692572</v>
       </c>
       <c r="J2" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K2" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04736185929999293</v>
+        <v>0.0451631141258223</v>
       </c>
       <c r="M2" t="n">
-        <v>5.014011704970658</v>
+        <v>5.01976812805308</v>
       </c>
       <c r="N2" t="n">
-        <v>40.74907797522137</v>
+        <v>40.81474486455155</v>
       </c>
       <c r="O2" t="n">
-        <v>6.383500448439036</v>
+        <v>6.388641863851154</v>
       </c>
       <c r="P2" t="n">
-        <v>331.0940218040446</v>
+        <v>331.1494120143091</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12455,28 +12489,28 @@
         <v>0.0747</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2861597981759126</v>
+        <v>0.2784274671258331</v>
       </c>
       <c r="J3" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K3" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08620561976481356</v>
+        <v>0.08185236516525085</v>
       </c>
       <c r="M3" t="n">
-        <v>5.319579249647496</v>
+        <v>5.333691385673151</v>
       </c>
       <c r="N3" t="n">
-        <v>44.69924587403706</v>
+        <v>44.98247816090986</v>
       </c>
       <c r="O3" t="n">
-        <v>6.685749462404126</v>
+        <v>6.706897804567315</v>
       </c>
       <c r="P3" t="n">
-        <v>324.8915805184054</v>
+        <v>324.974515146438</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12537,28 +12571,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2808612433703923</v>
+        <v>0.2731965729210505</v>
       </c>
       <c r="J4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08224894414496497</v>
+        <v>0.07805916565935755</v>
       </c>
       <c r="M4" t="n">
-        <v>5.365437986576376</v>
+        <v>5.381696862263831</v>
       </c>
       <c r="N4" t="n">
-        <v>45.32608822120738</v>
+        <v>45.60028721635187</v>
       </c>
       <c r="O4" t="n">
-        <v>6.732465240995112</v>
+        <v>6.752798472955629</v>
       </c>
       <c r="P4" t="n">
-        <v>327.3462909936816</v>
+        <v>327.4284999147162</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12615,28 +12649,28 @@
         <v>0.0931</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1639667486641481</v>
+        <v>0.1583656639096986</v>
       </c>
       <c r="J5" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K5" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03387300834976104</v>
+        <v>0.03173037936884837</v>
       </c>
       <c r="M5" t="n">
-        <v>5.024570234192004</v>
+        <v>5.032015925005833</v>
       </c>
       <c r="N5" t="n">
-        <v>39.48772073471324</v>
+        <v>39.58959245127485</v>
       </c>
       <c r="O5" t="n">
-        <v>6.283925583161631</v>
+        <v>6.292026100651113</v>
       </c>
       <c r="P5" t="n">
-        <v>334.7122837805551</v>
+        <v>334.7723593098724</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12674,7 +12708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F343"/>
+  <dimension ref="A1:F344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23653,6 +23687,38 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-35.50793573904996,174.47267370688732</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-35.50858012058793,174.4731090655879</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-35.509171746091866,174.4736372038346</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-35.50973753123725,174.47421078217664</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
